--- a/mosip_master/xlsx/zone.xlsx
+++ b/mosip_master/xlsx/zone.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="6900" tabRatio="500"/>
+    <workbookView windowWidth="20490" windowHeight="7500" tabRatio="500"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2670,9 +2670,9 @@
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:A48" etc:filterBottomFollowUsedRange="0">
     <filterColumn colId="0">
-      <filters>
-        <filter val="fra"/>
-      </filters>
+      <customFilters>
+        <customFilter operator="equal" val="fra"/>
+      </customFilters>
     </filterColumn>
     <extLst/>
   </autoFilter>
